--- a/Output/count_num_voxel/Visit 1/Visit 1_num_voxel.xlsx
+++ b/Output/count_num_voxel/Visit 1/Visit 1_num_voxel.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="11_514D422F8C385B5F2350DFA5FF012D16118A599E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B69B2B07-5188-4037-8039-52F3C7C0443A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="71" uniqueCount="36">
   <si>
     <t>Participant_ID</t>
   </si>
@@ -141,12 +141,15 @@
   </si>
   <si>
     <t>041</t>
+  </si>
+  <si>
+    <t>inferior lateral ventricles</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -161,7 +164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -169,12 +172,14 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -193,7 +198,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -344,7 +349,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -368,9 +373,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -394,7 +399,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -429,7 +434,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -447,7 +452,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -472,7 +477,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -508,616 +513,707 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.90625" customWidth="true"/>
+    <col min="2" max="2" width="6.90625" customWidth="true"/>
+    <col min="3" max="3" width="6.90625" customWidth="true"/>
+    <col min="4" max="4" width="6.90625" customWidth="true"/>
+    <col min="5" max="5" width="13.08984375" customWidth="true"/>
+    <col min="6" max="6" width="14.54296875" customWidth="true"/>
+    <col min="7" max="7" width="21.1796875" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="G1" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>415778</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>285564</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>269162</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>1364</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>23025</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="G2" s="0">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>529813</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>570028</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>373096</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>2611</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <v>57087</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="G3" s="0">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>418806</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>313325</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>348199</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <v>2027</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="0">
         <v>47223</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="G4" s="0">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>424286</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>375592</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>311476</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <v>2241</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <v>28248</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="G5" s="0">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>335204</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>295452</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <v>428587</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <v>1771</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>71235</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="G6" s="0">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>351568</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>328143</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0">
         <v>499941</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="0">
         <v>2166</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <v>64093</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="G7" s="0">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>382697</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>417603</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0">
         <v>419019</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="0">
         <v>2061</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <v>51770</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="G8" s="0">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>416715</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>332501</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0">
         <v>303819</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="0">
         <v>1903</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <v>33407</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="G9" s="0">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>522512</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <v>399811</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0">
         <v>245056</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="0">
         <v>1684</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="0">
         <v>31112</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="G10" s="0">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>418623</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0">
         <v>400849</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="0">
         <v>281249</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="0">
         <v>1842</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="0">
         <v>41017</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="G11" s="0">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="0">
         <v>549341</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0">
         <v>401667</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="0">
         <v>220761</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="0">
         <v>1193</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="0">
         <v>13841</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="G12" s="0">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="0">
         <v>219192</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0">
         <v>333997</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="0">
         <v>423573</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="0">
         <v>2154</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="0">
         <v>38657</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="G13" s="0">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="0">
         <v>353227</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0">
         <v>312160</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="0">
         <v>259800</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="0">
         <v>1759</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="0">
         <v>38962</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="G14" s="0">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="0">
         <v>412117</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0">
         <v>321820</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="0">
         <v>315005</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="0">
         <v>1947</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="0">
         <v>57846</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="G15" s="0">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="0">
         <v>565339</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="0">
         <v>423934</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="0">
         <v>171987</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="0">
         <v>1278</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="0">
         <v>21105</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="G16" s="0">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="0">
         <v>353964</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0">
         <v>287231</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="0">
         <v>260364</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="0">
         <v>1869</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="0">
         <v>26921</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="G17" s="0">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="0">
         <v>681026</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="0">
         <v>484599</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="0">
         <v>276086</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="0">
         <v>1654</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="0">
         <v>29450</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="G18" s="0">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="0">
         <v>509953</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="0">
         <v>401948</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="0">
         <v>248964</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="0">
         <v>1498</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="0">
         <v>33536</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+      <c r="G19" s="0">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="0">
         <v>460464</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="0">
         <v>321066</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="0">
         <v>194126</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="0">
         <v>1111</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="0">
         <v>18598</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+      <c r="G20" s="0">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="0">
         <v>588916</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="0">
         <v>404232</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="0">
         <v>198079</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="0">
         <v>1792</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="0">
         <v>28063</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="G21" s="0">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="0">
         <v>520194</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="0">
         <v>337978</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="0">
         <v>157504</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="0">
         <v>1378</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="0">
         <v>22566</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="G22" s="0">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="0">
         <v>529146</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="0">
         <v>336791</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="0">
         <v>233435</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="0">
         <v>1426</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="0">
         <v>44094</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+      <c r="G23" s="0">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="0">
         <v>352098</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="0">
         <v>307200</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="0">
         <v>248654</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="0">
         <v>1708</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="0">
         <v>32452</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+      <c r="G24" s="0">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="0">
         <v>525611</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="0">
         <v>467237</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="0">
         <v>255699</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="0">
         <v>1362</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="0">
         <v>20957</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
+      <c r="G25" s="0">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="0">
         <v>473439</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="0">
         <v>320973</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="0">
         <v>319175</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="0">
         <v>1576</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="0">
         <v>31363</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="G26" s="0">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="0">
         <v>589711</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="0">
         <v>491555</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="0">
         <v>224997</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="0">
         <v>1424</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="0">
         <v>21181</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
+      <c r="G27" s="0">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="0">
         <v>543306</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="0">
         <v>379898</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="0">
         <v>260280</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="0">
         <v>1228</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="0">
         <v>22957</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+      <c r="G28" s="0">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="0">
         <v>501077</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="0">
         <v>436812</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="0">
         <v>247005</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="0">
         <v>1237</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="0">
         <v>11406</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="G29" s="0">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="0">
         <v>503775</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="0">
         <v>375144</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="0">
         <v>427132</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="0">
         <v>1920</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="0">
         <v>54742</v>
+      </c>
+      <c r="G30" s="0">
+        <v>2954</v>
       </c>
     </row>
   </sheetData>
